--- a/ucc/ssr/Results/ucc_test/['Grid5*4'].xlsx
+++ b/ucc/ssr/Results/ucc_test/['Grid5*4'].xlsx
@@ -484,31 +484,31 @@
         <v>472</v>
       </c>
       <c r="E2" t="n">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F2" t="n">
         <v>536</v>
       </c>
       <c r="G2" t="n">
-        <v>44717</v>
+        <v>46470</v>
       </c>
       <c r="H2" t="n">
-        <v>276021</v>
+        <v>285987</v>
       </c>
       <c r="I2" t="n">
-        <v>146.4640958309174</v>
+        <v>89.22557902336121</v>
       </c>
       <c r="J2" t="n">
-        <v>7.531313419342041</v>
+        <v>4.664512872695923</v>
       </c>
       <c r="K2" t="n">
-        <v>131.4760656356812</v>
+        <v>80.29246950149536</v>
       </c>
       <c r="L2" t="n">
-        <v>3.833109140396118</v>
+        <v>2.504909038543701</v>
       </c>
       <c r="M2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         <v>821</v>
       </c>
       <c r="D3" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E3" t="n">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="F3" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G3" t="n">
-        <v>45124</v>
+        <v>49501</v>
       </c>
       <c r="H3" t="n">
-        <v>269370</v>
+        <v>295398</v>
       </c>
       <c r="I3" t="n">
-        <v>142.7732181549072</v>
+        <v>66.90368628501892</v>
       </c>
       <c r="J3" t="n">
-        <v>9.683796644210815</v>
+        <v>4.908899068832397</v>
       </c>
       <c r="K3" t="n">
-        <v>125.5172009468079</v>
+        <v>57.18831253051758</v>
       </c>
       <c r="L3" t="n">
-        <v>3.794511795043945</v>
+        <v>2.271130084991455</v>
       </c>
       <c r="M3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -573,25 +573,25 @@
         <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>5801</v>
+        <v>5745</v>
       </c>
       <c r="H4" t="n">
-        <v>36315</v>
+        <v>36035</v>
       </c>
       <c r="I4" t="n">
-        <v>9.121325254440308</v>
+        <v>7.354995012283325</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5651865005493164</v>
+        <v>0.326183557510376</v>
       </c>
       <c r="K4" t="n">
-        <v>7.631719827651978</v>
+        <v>6.174329042434692</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7906482219696045</v>
+        <v>0.757859468460083</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
@@ -610,34 +610,34 @@
         <v>1060</v>
       </c>
       <c r="D5" t="n">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="E5" t="n">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="F5" t="n">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G5" t="n">
-        <v>50416</v>
+        <v>50166</v>
       </c>
       <c r="H5" t="n">
-        <v>301148</v>
+        <v>296901</v>
       </c>
       <c r="I5" t="n">
-        <v>167.9103972911835</v>
+        <v>88.24855303764343</v>
       </c>
       <c r="J5" t="n">
-        <v>9.74325966835022</v>
+        <v>5.681583881378174</v>
       </c>
       <c r="K5" t="n">
-        <v>150.9886200428009</v>
+        <v>78.28186249732971</v>
       </c>
       <c r="L5" t="n">
-        <v>4.292498826980591</v>
+        <v>2.690264463424683</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -653,31 +653,31 @@
         <v>1321</v>
       </c>
       <c r="D6" t="n">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E6" t="n">
-        <v>1150</v>
+        <v>1134</v>
       </c>
       <c r="F6" t="n">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="G6" t="n">
-        <v>58864</v>
+        <v>55827</v>
       </c>
       <c r="H6" t="n">
-        <v>360658</v>
+        <v>339094</v>
       </c>
       <c r="I6" t="n">
-        <v>180.7940690517426</v>
+        <v>111.2357671260834</v>
       </c>
       <c r="J6" t="n">
-        <v>10.46543049812317</v>
+        <v>6.81340479850769</v>
       </c>
       <c r="K6" t="n">
-        <v>162.8207979202271</v>
+        <v>99.21808218955994</v>
       </c>
       <c r="L6" t="n">
-        <v>3.976080417633057</v>
+        <v>2.407087564468384</v>
       </c>
       <c r="M6" t="n">
         <v>17</v>
@@ -699,28 +699,28 @@
         <v>554</v>
       </c>
       <c r="E7" t="n">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="F7" t="n">
-        <v>491</v>
+        <v>519</v>
       </c>
       <c r="G7" t="n">
-        <v>40526</v>
+        <v>42797</v>
       </c>
       <c r="H7" t="n">
-        <v>244672</v>
+        <v>257315</v>
       </c>
       <c r="I7" t="n">
-        <v>143.2139151096344</v>
+        <v>82.37858891487122</v>
       </c>
       <c r="J7" t="n">
-        <v>7.152688264846802</v>
+        <v>4.740319728851318</v>
       </c>
       <c r="K7" t="n">
-        <v>129.9127743244171</v>
+        <v>73.58221125602722</v>
       </c>
       <c r="L7" t="n">
-        <v>3.193617820739746</v>
+        <v>2.058959722518921</v>
       </c>
       <c r="M7" t="n">
         <v>15</v>
@@ -739,34 +739,34 @@
         <v>386</v>
       </c>
       <c r="D8" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E8" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F8" t="n">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="G8" t="n">
-        <v>29385</v>
+        <v>25865</v>
       </c>
       <c r="H8" t="n">
-        <v>188868</v>
+        <v>168724</v>
       </c>
       <c r="I8" t="n">
-        <v>80.37317299842834</v>
+        <v>36.68401408195496</v>
       </c>
       <c r="J8" t="n">
-        <v>2.76521110534668</v>
+        <v>1.817089319229126</v>
       </c>
       <c r="K8" t="n">
-        <v>74.02347469329834</v>
+        <v>32.88705968856812</v>
       </c>
       <c r="L8" t="n">
-        <v>2.34570050239563</v>
+        <v>1.354044675827026</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -782,34 +782,34 @@
         <v>976</v>
       </c>
       <c r="D9" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E9" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F9" t="n">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="G9" t="n">
-        <v>42803</v>
+        <v>45980</v>
       </c>
       <c r="H9" t="n">
-        <v>273462</v>
+        <v>295649</v>
       </c>
       <c r="I9" t="n">
-        <v>127.1589441299438</v>
+        <v>81.49547219276428</v>
       </c>
       <c r="J9" t="n">
-        <v>9.261747121810913</v>
+        <v>4.441304683685303</v>
       </c>
       <c r="K9" t="n">
-        <v>112.4124596118927</v>
+        <v>73.35250163078308</v>
       </c>
       <c r="L9" t="n">
-        <v>3.133985996246338</v>
+        <v>1.936596393585205</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -825,34 +825,34 @@
         <v>719</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E10" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F10" t="n">
-        <v>596</v>
+        <v>446</v>
       </c>
       <c r="G10" t="n">
-        <v>77699</v>
+        <v>56380</v>
       </c>
       <c r="H10" t="n">
-        <v>483911</v>
+        <v>349539</v>
       </c>
       <c r="I10" t="n">
-        <v>204.5920331478119</v>
+        <v>94.02775311470032</v>
       </c>
       <c r="J10" t="n">
-        <v>11.58007907867432</v>
+        <v>5.668658494949341</v>
       </c>
       <c r="K10" t="n">
-        <v>177.9832403659821</v>
+        <v>80.98443531990051</v>
       </c>
       <c r="L10" t="n">
-        <v>5.152357578277588</v>
+        <v>2.389119386672974</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -871,31 +871,31 @@
         <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>5160</v>
+        <v>4865</v>
       </c>
       <c r="H11" t="n">
-        <v>30114</v>
+        <v>28346</v>
       </c>
       <c r="I11" t="n">
-        <v>21.73082113265991</v>
+        <v>7.166751146316528</v>
       </c>
       <c r="J11" t="n">
-        <v>0.694279670715332</v>
+        <v>0.2797379493713379</v>
       </c>
       <c r="K11" t="n">
-        <v>19.96012282371521</v>
+        <v>6.540047407150269</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8808639049530029</v>
+        <v>0.2516458034515381</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ucc/ssr/Results/ucc_test/['Grid5*4'].xlsx
+++ b/ucc/ssr/Results/ucc_test/['Grid5*4'].xlsx
@@ -481,34 +481,34 @@
         <v>918</v>
       </c>
       <c r="D2" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E2" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F2" t="n">
-        <v>536</v>
+        <v>469</v>
       </c>
       <c r="G2" t="n">
-        <v>46470</v>
+        <v>39725</v>
       </c>
       <c r="H2" t="n">
-        <v>285987</v>
+        <v>243069</v>
       </c>
       <c r="I2" t="n">
-        <v>89.22557902336121</v>
+        <v>82.55197215080261</v>
       </c>
       <c r="J2" t="n">
-        <v>4.664512872695923</v>
+        <v>4.288571834564209</v>
       </c>
       <c r="K2" t="n">
-        <v>80.29246950149536</v>
+        <v>73.92019438743591</v>
       </c>
       <c r="L2" t="n">
-        <v>2.504909038543701</v>
+        <v>2.758823156356812</v>
       </c>
       <c r="M2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -524,31 +524,31 @@
         <v>821</v>
       </c>
       <c r="D3" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E3" t="n">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="F3" t="n">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="G3" t="n">
-        <v>49501</v>
+        <v>52252</v>
       </c>
       <c r="H3" t="n">
-        <v>295398</v>
+        <v>315082</v>
       </c>
       <c r="I3" t="n">
-        <v>66.90368628501892</v>
+        <v>71.40770268440247</v>
       </c>
       <c r="J3" t="n">
-        <v>4.908899068832397</v>
+        <v>5.572888135910034</v>
       </c>
       <c r="K3" t="n">
-        <v>57.18831253051758</v>
+        <v>59.95674705505371</v>
       </c>
       <c r="L3" t="n">
-        <v>2.271130084991455</v>
+        <v>3.179246187210083</v>
       </c>
       <c r="M3" t="n">
         <v>17</v>
@@ -573,28 +573,28 @@
         <v>125</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>5745</v>
+        <v>6002</v>
       </c>
       <c r="H4" t="n">
-        <v>36035</v>
+        <v>37169</v>
       </c>
       <c r="I4" t="n">
-        <v>7.354995012283325</v>
+        <v>10.1865541934967</v>
       </c>
       <c r="J4" t="n">
-        <v>0.326183557510376</v>
+        <v>0.4602522850036621</v>
       </c>
       <c r="K4" t="n">
-        <v>6.174329042434692</v>
+        <v>7.980781316757202</v>
       </c>
       <c r="L4" t="n">
-        <v>0.757859468460083</v>
+        <v>1.59060263633728</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -610,34 +610,34 @@
         <v>1060</v>
       </c>
       <c r="D5" t="n">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="E5" t="n">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="F5" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G5" t="n">
-        <v>50166</v>
+        <v>50925</v>
       </c>
       <c r="H5" t="n">
-        <v>296901</v>
+        <v>301430</v>
       </c>
       <c r="I5" t="n">
-        <v>88.24855303764343</v>
+        <v>100.3391871452332</v>
       </c>
       <c r="J5" t="n">
-        <v>5.681583881378174</v>
+        <v>6.145331144332886</v>
       </c>
       <c r="K5" t="n">
-        <v>78.28186249732971</v>
+        <v>88.70937037467957</v>
       </c>
       <c r="L5" t="n">
-        <v>2.690264463424683</v>
+        <v>3.20810079574585</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -653,34 +653,34 @@
         <v>1321</v>
       </c>
       <c r="D6" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E6" t="n">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="F6" t="n">
-        <v>672</v>
+        <v>728</v>
       </c>
       <c r="G6" t="n">
-        <v>55827</v>
+        <v>61973</v>
       </c>
       <c r="H6" t="n">
-        <v>339094</v>
+        <v>380183</v>
       </c>
       <c r="I6" t="n">
-        <v>111.2357671260834</v>
+        <v>113.172376871109</v>
       </c>
       <c r="J6" t="n">
-        <v>6.81340479850769</v>
+        <v>7.522650480270386</v>
       </c>
       <c r="K6" t="n">
-        <v>99.21808218955994</v>
+        <v>99.44742965698242</v>
       </c>
       <c r="L6" t="n">
-        <v>2.407087564468384</v>
+        <v>3.567090272903442</v>
       </c>
       <c r="M6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -696,34 +696,34 @@
         <v>1020</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="E7" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F7" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="G7" t="n">
-        <v>42797</v>
+        <v>41029</v>
       </c>
       <c r="H7" t="n">
-        <v>257315</v>
+        <v>242502</v>
       </c>
       <c r="I7" t="n">
-        <v>82.37858891487122</v>
+        <v>79.49075293540955</v>
       </c>
       <c r="J7" t="n">
-        <v>4.740319728851318</v>
+        <v>4.37316632270813</v>
       </c>
       <c r="K7" t="n">
-        <v>73.58221125602722</v>
+        <v>70.74739265441895</v>
       </c>
       <c r="L7" t="n">
-        <v>2.058959722518921</v>
+        <v>2.75533127784729</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -739,34 +739,34 @@
         <v>386</v>
       </c>
       <c r="D8" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E8" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F8" t="n">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="G8" t="n">
-        <v>25865</v>
+        <v>19929</v>
       </c>
       <c r="H8" t="n">
-        <v>168724</v>
+        <v>128481</v>
       </c>
       <c r="I8" t="n">
-        <v>36.68401408195496</v>
+        <v>26.52469897270203</v>
       </c>
       <c r="J8" t="n">
-        <v>1.817089319229126</v>
+        <v>1.309799671173096</v>
       </c>
       <c r="K8" t="n">
-        <v>32.88705968856812</v>
+        <v>22.82856416702271</v>
       </c>
       <c r="L8" t="n">
-        <v>1.354044675827026</v>
+        <v>1.999310731887817</v>
       </c>
       <c r="M8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -782,34 +782,34 @@
         <v>976</v>
       </c>
       <c r="D9" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="E9" t="n">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="F9" t="n">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="G9" t="n">
-        <v>45980</v>
+        <v>43661</v>
       </c>
       <c r="H9" t="n">
-        <v>295649</v>
+        <v>275780</v>
       </c>
       <c r="I9" t="n">
-        <v>81.49547219276428</v>
+        <v>74.69803786277771</v>
       </c>
       <c r="J9" t="n">
-        <v>4.441304683685303</v>
+        <v>4.83165717124939</v>
       </c>
       <c r="K9" t="n">
-        <v>73.35250163078308</v>
+        <v>65.635897397995</v>
       </c>
       <c r="L9" t="n">
-        <v>1.936596393585205</v>
+        <v>2.755258083343506</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -825,34 +825,34 @@
         <v>719</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E10" t="n">
-        <v>693</v>
+        <v>706</v>
       </c>
       <c r="F10" t="n">
-        <v>446</v>
+        <v>319</v>
       </c>
       <c r="G10" t="n">
-        <v>56380</v>
+        <v>41306</v>
       </c>
       <c r="H10" t="n">
-        <v>349539</v>
+        <v>256425</v>
       </c>
       <c r="I10" t="n">
-        <v>94.02775311470032</v>
+        <v>64.90214085578918</v>
       </c>
       <c r="J10" t="n">
-        <v>5.668658494949341</v>
+        <v>4.485852479934692</v>
       </c>
       <c r="K10" t="n">
-        <v>80.98443531990051</v>
+        <v>55.38636589050293</v>
       </c>
       <c r="L10" t="n">
-        <v>2.389119386672974</v>
+        <v>1.823959350585938</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -871,28 +871,28 @@
         <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>4865</v>
+        <v>5014</v>
       </c>
       <c r="H11" t="n">
-        <v>28346</v>
+        <v>29073</v>
       </c>
       <c r="I11" t="n">
-        <v>7.166751146316528</v>
+        <v>7.617071151733398</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2797379493713379</v>
+        <v>0.2886881828308105</v>
       </c>
       <c r="K11" t="n">
-        <v>6.540047407150269</v>
+        <v>6.936389446258545</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2516458034515381</v>
+        <v>0.3024311065673828</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
